--- a/data/trans_bre/IP21B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Clase-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 0,0</t>
+          <t>-68,84; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-70,98; 68,61</t>
+          <t>-73,53; 61,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-82,77; 64,17</t>
+          <t>-82,77; 73,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 0,0</t>
+          <t>-82,03; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,56</t>
+          <t>0,0; 39,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 21,72</t>
+          <t>-30,94; 22,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 55,72</t>
+          <t>-51,15; 50,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,42; 0,0</t>
+          <t>-71,78; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 383,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,34</t>
+          <t>0,0; 74,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 43,32</t>
+          <t>-33,65; 43,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 41,15</t>
+          <t>-52,31; 36,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,79; 0,0</t>
+          <t>-66,95; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 0,0</t>
+          <t>-57,43; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 6,29</t>
+          <t>-17,44; 4,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 13,2</t>
+          <t>-21,3; 10,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 25,16</t>
+          <t>-19,47; 23,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 31,78</t>
+          <t>-30,15; 32,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,17</t>
+          <t>-100,0; 158,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-77,77; 131,27</t>
+          <t>-77,13; 116,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 281,79</t>
+          <t>-64,26; 228,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-94,78; 337,47</t>
+          <t>-82,54; 492,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Clase-trans_bre.xlsx
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 61,92</t>
+          <t>-72,39; 61,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-82,77; 73,66</t>
+          <t>-83,48; 64,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 0,0</t>
+          <t>-83,55; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,25</t>
+          <t>0,0; 39,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 22,09</t>
+          <t>-27,06; 22,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,15; 50,36</t>
+          <t>-51,25; 50,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,78; 0,0</t>
+          <t>-63,48; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,76; 504,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,55</t>
+          <t>0,0; 75,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 43,71</t>
+          <t>-31,47; 52,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 36,2</t>
+          <t>-51,39; 44,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,1; 506,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 0,0</t>
+          <t>-57,06; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 4,6</t>
+          <t>-16,14; 7,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 10,61</t>
+          <t>-21,11; 9,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 23,48</t>
+          <t>-18,21; 25,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 32,53</t>
+          <t>-33,12; 29,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,48</t>
+          <t>-100,0; 369,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 116,7</t>
+          <t>-78,36; 96,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 228,64</t>
+          <t>-62,58; 222,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 492,8</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,83</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,68%</t>
+          <t>-3,75%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 0,0</t>
+          <t>-68,4; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 61,92</t>
+          <t>-70,98; 68,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-83,48; 64,47</t>
+          <t>-82,45; 69,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>35,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-83,55; 0,0</t>
+          <t>-82,12; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-16,89</t>
+          <t>-18,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,32</t>
+          <t>0,0; 56,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 22,8</t>
+          <t>-30,2; 21,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 50,62</t>
+          <t>-48,76; 55,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 0,0</t>
+          <t>-72,11; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,76; 504,22</t>
+          <t>-89,67; 383,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36,87</t>
+          <t>39,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,44</t>
+          <t>0,0; 75,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 52,0</t>
+          <t>-36,67; 43,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 44,88</t>
+          <t>-56,81; 41,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 506,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 0,0</t>
+          <t>-62,79; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 0,0</t>
+          <t>-57,12; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 7,18</t>
+          <t>-17,3; 6,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 9,73</t>
+          <t>-19,03; 13,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 25,65</t>
+          <t>-17,77; 25,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 29,51</t>
+          <t>-32,09; 34,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 369,04</t>
+          <t>-100,0; 217,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 96,29</t>
+          <t>-77,77; 131,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 222,74</t>
+          <t>-57,99; 281,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 367,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP21B-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,153 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-17,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-33,98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-7,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-3,75%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-17.63373181228037</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-33.98180332091321</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.359230164085663</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.310955127543956</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.07872908962805233</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.03751335444358383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-68,4; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-70,98; 68,61</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-82,45; 69,88</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-68.40363092323531</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-70.97857553941272</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-82.4508320907216</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>68.60954626103526</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>76.26329566904953</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-25,18</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,26</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-77,1; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>-25.17534477527355</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>35.25932287309409</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-24,62</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-32,68</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-77.09879459214126</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-82,12; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +773,159 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,99</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-18,57</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-3,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-24.6236274038844</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-32.67807723355237</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 56,56</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-30,2; 21,72</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-48,76; 55,72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-72,11; 0,0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-89,67; 383,87</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-82.12194946907434</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>16,81</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,14</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-14,85%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 75,34</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-36,67; 43,32</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-56,81; 41,15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>9.986344371370063</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.6749344808114677</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6722831212319258</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-18.57231266588346</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.03513833387481788</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.02012780470586259</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-15,08</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-14,65</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31,88</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-30.2001054513834</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-48.75606373872871</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-72.11405553797742</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.8967280124640946</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-62,79; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-57,12; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>56.55528934979325</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.71703524663704</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>55.72103527384555</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>3.838706562369525</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,44 +933,32 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-5,63</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-5,57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-51,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-29,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
+      <c r="C16" s="5" t="n">
+        <v>16.80506956494815</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.16642581427187</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-6.137137686144473</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>39.1426497074149</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.009272711317423705</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1484849569497996</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -1255,52 +966,226 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-17,3; 6,29</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-19,03; 13,2</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-17,77; 25,16</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-32,09; 34,39</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 217,17</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-77,77; 131,27</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-57,99; 281,79</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 367,54</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-36.67368103787125</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-56.8143939708801</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>75.33618434232572</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>43.31900104145848</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>41.15359621982748</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-15.08137090933825</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-14.65088662502851</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>31.88421993439479</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-62.78942713884711</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-57.11522167961351</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-5.626794505444352</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-5.568589576350291</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3.639883869219487</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.1949990453929296</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.5168511775231556</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.2905369982246296</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.1714578647305999</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.007363632267357125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-17.30264034807078</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-19.03071094199859</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-17.77219467278182</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-32.08569542076016</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.7776507812125412</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.5798640387538986</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.289844748473151</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>13.20145618264647</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>25.16443066903274</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>34.38706574460353</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>2.171665526792934</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.312723557202744</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>2.817932546411605</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>3.67537607925836</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1193,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
